--- a/branches/release/v2027.0.0-ballot.rc2/ValueSet-mii-vs-lufu-lnc-rv.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/ValueSet-mii-vs-lufu-lnc-rv.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01</t>
+    <t>2026-09-02</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release/v2027.0.0-ballot.rc2/ValueSet-mii-vs-lufu-lnc-rv.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/ValueSet-mii-vs-lufu-lnc-rv.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>

--- a/branches/release/v2027.0.0-ballot.rc2/ValueSet-mii-vs-lufu-lnc-rv.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/ValueSet-mii-vs-lufu-lnc-rv.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
   <si>
     <t>Property</t>
   </si>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Import the ValueSet for lungfunction reserve volume</t>
+    <t>Import the ValueSet for lungfunction Residual Volume</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -105,34 +105,46 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>19924-0</t>
-  </si>
-  <si>
-    <t>Expiratory reserve</t>
-  </si>
-  <si>
-    <t>19923-2</t>
-  </si>
-  <si>
-    <t>Expiratory reserve Predicted</t>
-  </si>
-  <si>
-    <t>100759-0</t>
-  </si>
-  <si>
-    <t>Inspiratory reserve [Volume] Respiratory system by Spirometry</t>
-  </si>
-  <si>
-    <t>19921-6</t>
-  </si>
-  <si>
-    <t>Expiratory reserve by Helium rebreathing</t>
-  </si>
-  <si>
-    <t>19922-4</t>
-  </si>
-  <si>
-    <t>Expiratory reserve by Helium single breath</t>
+    <t>20146-7</t>
+  </si>
+  <si>
+    <t>Residual volume</t>
+  </si>
+  <si>
+    <t>20145-9</t>
+  </si>
+  <si>
+    <t>Residual volume Predicted</t>
+  </si>
+  <si>
+    <t>20143-4</t>
+  </si>
+  <si>
+    <t>Residual volume by Helium rebreathing</t>
+  </si>
+  <si>
+    <t>81453-3</t>
+  </si>
+  <si>
+    <t>Residual volume --post bronchodilation</t>
+  </si>
+  <si>
+    <t>81452-5</t>
+  </si>
+  <si>
+    <t>Residual volume --pre bronchodilation</t>
+  </si>
+  <si>
+    <t>20144-2</t>
+  </si>
+  <si>
+    <t>Residual volume by Helium single breath</t>
+  </si>
+  <si>
+    <t>94125-2</t>
+  </si>
+  <si>
+    <t>Residual volume/Predicted by Plethysmograph body box</t>
   </si>
   <si>
     <t/>
@@ -407,7 +419,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -467,15 +479,31 @@
         <v>40</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
